--- a/data/seed/portfolio/L-2025-8946/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-8946/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J149"/>
+  <dimension ref="A1:J171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,141 +542,141 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>15063000</v>
+        <v>6627000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №208/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №7209 за поставленный товар</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>143463000</v>
+        <v>135027000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>8624000</v>
+        <v>119481000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №34/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №6905 от 02.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>152087000</v>
+        <v>254508000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>30458000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>24614000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>211882155</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000415259485001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3748 03.07.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №241</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>182545000</v>
+        <v>229894000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>172056000</v>
+        <v>14018000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Durdona Yog' Zavodi MChJ</t>
+          <t>Bekobod Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>312489938</t>
+          <t>288081838</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000441885782001</t>
+          <t>20208000059480364001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -686,37 +686,37 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №427</t>
+          <t>Оплата по с/ф №9188 за поставленный товар</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>354601000</v>
+        <v>243912000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>11511000</v>
+        <v>5620000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Durdona Yog' Zavodi MChJ</t>
+          <t>Bekobod Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>312489938</t>
+          <t>288081838</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000441885782001</t>
+          <t>20208000059480364001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -726,51 +726,51 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8049 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №8240 от 03.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>366112000</v>
+        <v>249532000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>8093000</v>
+        <v>5372000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ziyo Polimer AJ</t>
+          <t>Bekobod Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>320880818</t>
+          <t>288081838</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000860594803001</t>
+          <t>20208000059480364001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shartnoma №295/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, h/f №8044 03.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>374205000</v>
+        <v>254904000</v>
       </c>
     </row>
     <row r="14">
@@ -780,37 +780,37 @@
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>20425000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>5988000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №67/26</t>
+          <t>Оплата по счет-фактуре №26 за поставленный товар</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>353780000</v>
+        <v>260892000</v>
       </c>
     </row>
     <row r="15">
@@ -820,98 +820,98 @@
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>25695000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>3700000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Durdona Moy XK</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ish haqi, reestr №4006</t>
+          <t>Оплата за товар по счет-фактуре №2417 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>328085000</v>
+        <v>264592000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>14976000</v>
+        <v>3118000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shartnoma №155/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №4837 за поставленный товар</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>343061000</v>
+        <v>267710000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>16564000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>25695000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ilhom Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>380028234</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000449433319001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -921,197 +921,197 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8830</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>359625000</v>
+        <v>242015000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>4857000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>31340000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Durdona Yog' Zavodi MChJ</t>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>312489938</t>
+          <t>231709008</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000441885782001</t>
+          <t>20208000768612620001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shartnoma №266/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №256/26</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>364482000</v>
+        <v>210675000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>3680000</v>
+        <v>75070000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shahrisabz Qurilish Materiallari AJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>374593064</t>
+          <t>286584545</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000122515239001</t>
+          <t>20208000782827859001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Предоплата за материалы по дг. №140/26</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>360802000</v>
+        <v>135605000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>37315000</v>
+        <v>3680000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Shahrisabz Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>310118821</t>
+          <t>259306401</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000514152594001</t>
+          <t>20208000251523904001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №243/26, QQS BILAN</t>
+          <t>Арендная плата за июль 226 г. по договору №33/20</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>323487000</v>
+        <v>131925000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
-        <v>7736000</v>
+        <v>10459000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8616 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №7742 за поставленный товар</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>331223000</v>
+        <v>142384000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>23720000</v>
-      </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n">
+        <v>5297000</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Denov Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>310118821</t>
+          <t>352108361</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000514152594001</t>
+          <t>20208000265559873001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1121,157 +1121,157 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №76/26</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №61/26 ОТ 08.07.2026</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>307503000</v>
+        <v>147681000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>16370000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>21149000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №119/26 от 13.07.2026, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №3876 от 10.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>291133000</v>
+        <v>168830000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>3504000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>7903000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyun 2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7797</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>287629000</v>
+        <v>176733000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>3504000</v>
+        <v>37487000</v>
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>231709008</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000768612620001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
+          <t>Оплата за товары согласно с/ф №3718</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>284125000</v>
+        <v>139246000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>17664000</v>
+        <v>48082000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ziyo Polimer AJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>320880818</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000860594803001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1281,947 +1281,957 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6438</t>
+          <t>Shartnoma №18/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>301789000</v>
+        <v>187328000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46219</v>
+        <v>46216</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>20553000</v>
+        <v>4528000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Shartnoma №184/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №258/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>322342000</v>
+        <v>191856000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46219</v>
+        <v>46216</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>16983000</v>
+        <v>3372000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №117/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №11/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>339325000</v>
+        <v>195228000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46219</v>
+        <v>46216</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>139214000</v>
+        <v>12748000</v>
       </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>231709008</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000768612620001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №119/26, QQS bilan</t>
+          <t>Оплата за сырье по договору №271/26 от 13.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>200111000</v>
+        <v>182480000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46220</v>
+        <v>46216</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>9544000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>95118000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bekobod Agro Servis XK</t>
+          <t>Nurafshon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>225729517</t>
+          <t>243619119</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000665211036001</t>
+          <t>20208000104819736001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5076 от 17.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №4551</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>209655000</v>
+        <v>87362000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>16044000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>11668000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Denov Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>352108361</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000265559873001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1087</t>
+          <t>Mahsulot uchun to'lov, shartnoma №231/26, QQS 12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>193611000</v>
+        <v>99030000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>121464000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>7647000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Oltin Vodiy Avto Savdo XK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>310118821</t>
+          <t>202823474</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000514152594001</t>
+          <t>20208000943331944001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №166/26</t>
+          <t>Tovar uchun to'lov, h/f №1888 14.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>72147000</v>
+        <v>106677000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46223</v>
+        <v>46217</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>6414000</v>
+        <v>4438000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №7295</t>
+          <t>Mahsulot uchun to'lov, shartn. №126/26, QQS 12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>78561000</v>
+        <v>111115000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>6121000</v>
+        <v>8621000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Durdona Yog' Zavodi MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>312489938</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000441885782001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №44/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №5663 за поставленный товар</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>84682000</v>
+        <v>119736000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46224</v>
+        <v>46218</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>6656000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>7993000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Оплата по счет-фактуре №6931 за поставленный товар</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>78026000</v>
+        <v>127729000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46224</v>
+        <v>46219</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>36860000</v>
+        <v>3504000</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №266/26</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>41166000</v>
+        <v>124225000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46225</v>
+        <v>46219</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n">
-        <v>23200000</v>
-      </c>
+      <c r="C37" s="2" t="n">
+        <v>3504000</v>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Durdona Yog' Zavodi MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>312489938</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000441885782001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6085</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>64366000</v>
+        <v>120721000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46226</v>
+        <v>46220</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>4491000</v>
+        <v>6081000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7142 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №8212 от 17.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>68857000</v>
+        <v>126802000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46227</v>
+        <v>46223</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>2300000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>14271000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000403566227001</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Оплата за продукцию по договору №166/26, НДС 12%</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>66557000</v>
+        <v>141073000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46228</v>
+        <v>46223</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>27900000</v>
-      </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n">
+        <v>11792000</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-8946)</t>
+          <t>Durdona Moy XK</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>16307000267556002417</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-8946 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата по с/ф №4169 за поставленный товар</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>38657000</v>
+        <v>152865000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>19384000</v>
+        <v>10399000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Bekobod Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>288081838</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000059480364001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Shartnoma №125/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №248/26, НДС 12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>58041000</v>
+        <v>163264000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n">
-        <v>11071000</v>
-      </c>
+      <c r="C42" s="2" t="n">
+        <v>20268000</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Durdona Yog' Zavodi MChJ</t>
+          <t>Termiz Plastik MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>312489938</t>
+          <t>372951786</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000441885782001</t>
+          <t>20208000521103661001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2470</t>
+          <t>Оплата за товары согласно счет-фактуре №3053</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>69112000</v>
+        <v>142996000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n">
-        <v>6380000</v>
-      </c>
+      <c r="C43" s="2" t="n">
+        <v>8978000</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>231709008</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000768612620001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Shartnoma №279/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №8466</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>75492000</v>
+        <v>134018000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46231</v>
+        <v>46226</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>69245000</v>
+        <v>26209000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ziyo Polimer AJ</t>
+          <t>Bekobod Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>320880818</t>
+          <t>288081838</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000860594803001</t>
+          <t>20208000059480364001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №7127</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №6131</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>144737000</v>
+        <v>160227000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46231</v>
+        <v>46226</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>37745000</v>
+        <v>17008000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №634</t>
+          <t>Mahsulot uchun to'lov, shartn. №45/26, QQS 12%</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>182482000</v>
+        <v>177235000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46232</v>
+        <v>46226</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>15916000</v>
+        <v>11502000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Bekobod Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>288081838</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000059480364001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №116/26 от 29.07.2026</t>
+          <t>Оплата по с/ф №9859 за поставленный товар</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>198398000</v>
+        <v>188737000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>7687000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Durdona Moy XK</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6917 23.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>198098000</v>
+        <v>196424000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>33571000</v>
+        <v>6040000</v>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Termiz Qurilish Materiallari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>339985857</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000510257966001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2276</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>164527000</v>
+        <v>190384000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46237</v>
+        <v>46227</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>45991000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Afrosiyob Avto Savdo MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>388110938</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000621343308001</t>
+          <t>20208000356622702001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Shartnoma №112/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>210518000</v>
+        <v>188084000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46237</v>
+        <v>46227</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>12036000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>9007000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bekobod Agro Servis XK</t>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>225729517</t>
+          <t>231709008</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000665211036001</t>
+          <t>20208000768612620001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2231,312 +2241,312 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Shartnoma №202/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по дог. №21/26 от 24.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>222554000</v>
+        <v>179077000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46238</v>
+        <v>46228</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>16418000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>27900000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bekobod Dori-Darmon XK</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>390595671</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-8946)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000807937872001</t>
+          <t>16307000267556002417</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, hartnoma №112/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2025-8946 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>238972000</v>
+        <v>151177000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46238</v>
+        <v>46230</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>25438000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>16110000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №3074</t>
+          <t>Оплата за товар по счет-фактуре №3138 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>213534000</v>
+        <v>167287000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46239</v>
+        <v>46230</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>34435000</v>
+        <v>11052000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №8688 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №5584 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>247969000</v>
+        <v>178339000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46239</v>
+        <v>46230</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>5073000</v>
+        <v>69877000</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>231709008</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000768612620001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №248/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №7126</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>242896000</v>
+        <v>108462000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46241</v>
+        <v>46231</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>3644000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>13460000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Shahrisabz Qurilish Materiallari AJ</t>
+          <t>Oltin Vodiy Avto Savdo XK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>374593064</t>
+          <t>202823474</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000122515239001</t>
+          <t>20208000943331944001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov avgust</t>
+          <t>Оплата за продукцию по договору №261/26, НДС 12%</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>239252000</v>
+        <v>121922000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46244</v>
+        <v>46231</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>58010000</v>
+        <v>4250000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yulduz Logistik MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>333317090</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000867686126001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №232/26, QQS 12%</t>
+          <t>Оплат по с/ф №5896 за поставленный товар</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>297262000</v>
+        <v>126172000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46244</v>
+        <v>46232</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>4699000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>9036000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №1305</t>
+          <t>Оплата за продукцию по договору №60/26, НДС 12%</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>292563000</v>
+        <v>135208000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46244</v>
+        <v>46232</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>307555000</v>
+        <v>24387000</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Durdona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>211882155</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000415259485001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2546,357 +2556,352 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №162/26</t>
+          <t>Предоплата за материалы по договору №206/26</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>-14992000</v>
+        <v>110821000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46248</v>
+        <v>46233</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>3469000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>18240000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Оплата за продукцию по договору №232/26, НДС 12%</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>-18461000</v>
+        <v>129061000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46248</v>
+        <v>46233</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>3469000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>12265000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Shartnoma №178/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>-21930000</v>
+        <v>141326000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46251</v>
+        <v>46233</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>38741000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>18204000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>231709008</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000768612620001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Shartnoma №142/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №88/26</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>16811000</v>
+        <v>123122000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46251</v>
+        <v>46234</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>4446000</v>
-      </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n">
+        <v>4454000</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №238/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6096</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>12365000</v>
+        <v>127576000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46251</v>
+        <v>46234</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>10378000</v>
-      </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n">
+        <v>4430000</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №190/26</t>
+          <t>Оплата по счет-фактуре №2127 за поставленный товар</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1987000</v>
+        <v>132006000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46251</v>
+        <v>46234</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>16576000</v>
+        <v>300000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>310118821</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000514152594001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №237/26, QQS bilan</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>-14589000</v>
+        <v>131706000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46252</v>
+        <v>46237</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>21658000</v>
+        <v>45048000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7196 18.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №93/26 от 03.08.2026</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>7069000</v>
+        <v>176754000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46252</v>
+        <v>46237</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>10827000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>15816000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №256/26</t>
+          <t>Оплата за продукцию по договору №200/26, НДС 12%</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>-3758000</v>
+        <v>192570000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46252</v>
+        <v>46237</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>17536000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>12415000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bekobod Qog'oz MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>241436191</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000901048197001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2906,667 +2911,672 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №154/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №1881 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>-21294000</v>
+        <v>204985000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46253</v>
+        <v>46237</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>25313000</v>
+        <v>11288000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Urganch Qog'oz AJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>259567198</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000793787232001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>MAHSLOT UCHUN TO'LOV, SHARTNOMA №125/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7404 03.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>4019000</v>
+        <v>216273000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46253</v>
+        <v>46237</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>22487000</v>
+        <v>3265000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №122/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №142/26 от 03.08.2026</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>26506000</v>
+        <v>219538000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46253</v>
+        <v>46237</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>19287000</v>
-      </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n">
+        <v>3193000</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Jizzax Mebel MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>365971740</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000132706714001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №4/26</t>
+          <t>Оплата за продукцию по договору №9/26, НДС 12%</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>7219000</v>
+        <v>222731000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46254</v>
+        <v>46237</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n">
-        <v>54270000</v>
-      </c>
+      <c r="C71" s="2" t="n">
+        <v>10242000</v>
+      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>231709008</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000768612620001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Shartnoma №136/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №220/26</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>61489000</v>
+        <v>212489000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46254</v>
+        <v>46237</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>41434000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>96439000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Durdona Yog' Zavodi MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>312489938</t>
+          <t>286584545</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000441885782001</t>
+          <t>20208000782827859001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun o'lov h/f №995</t>
+          <t>Оплата за транспортные услуги по договору №79/26</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>102923000</v>
+        <v>116050000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46255</v>
+        <v>46238</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>24933000</v>
+        <v>6795000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4298 21.08.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №8493 за поставленный товар</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>127856000</v>
+        <v>122845000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46255</v>
+        <v>46238</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>16600000</v>
+        <v>2986000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bekobod Dori-Darmon XK</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>390595671</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000807937872001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8825</t>
+          <t>Оплата за продукцию по договору №27/26, НДС 12%</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>144456000</v>
+        <v>125831000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46258</v>
+        <v>46238</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>5997000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>2579000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Urganch Qog'oz AJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>259567198</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000793787232001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Оплата за продукцию по дог. №113/26, НДС 12%</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>138459000</v>
+        <v>128410000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46258</v>
+        <v>46238</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>8152000</v>
+        <v>25438000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Termiz Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>339985857</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000510257966001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9436</t>
+          <t>ПЕРЕЧИСЛЕНИЕ ЗАРАБОТНОЙ ПЛАТЫ ЗА ИЮЛЬ 2026 Г. СОГЛАСНО РЕЕСТРУ №4395</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>130307000</v>
+        <v>102972000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46258</v>
+        <v>46240</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>20303000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>5247000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>310118821</t>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000514152594001</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №201/26, QQS BILAN</t>
+          <t>Предоплата за товар по дог. №6/26 от 06.08.2026</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>110004000</v>
+        <v>108219000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46259</v>
+        <v>46241</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>27900000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>14631000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-8946)</t>
+          <t>Durdona Moy XK</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>16307000267556002417</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-8946 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №349 ОТ 07.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>82104000</v>
+        <v>122850000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46261</v>
+        <v>46241</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>2277000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>5669000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000403566227001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата по счет-фактуре №4809 за поставленный товар</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>79827000</v>
+        <v>128519000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46265</v>
+        <v>46241</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>31954000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>3644000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bekobod Dori-Darmon XK</t>
+          <t>Shahrisabz Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>390595671</t>
+          <t>259306401</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000807937872001</t>
+          <t>20208000251523904001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3951 31.08.2026, QQS bilan</t>
+          <t>Аренда помещения за август, дог. №33/20</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>111781000</v>
+        <v>124875000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>23428000</v>
+        <v>9095000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Ishonch Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>390403372</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000469368665001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №566 31.08.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №72/26, QQS 12%</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>135209000</v>
+        <v>133970000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>18519000</v>
+        <v>6680000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №143/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №8251 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>153728000</v>
+        <v>140650000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>13559000</v>
+        <v>2517000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №248/26 ОТ 31.08.2026</t>
+          <t>Оплата за товар по счет-фактуре №160 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>167287000</v>
+        <v>143167000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>300000</v>
+        <v>10501000</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>286584545</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000782827859001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3576,237 +3586,237 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Оплата за товары согласно счет-фактуре №6705</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>166987000</v>
+        <v>132666000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>22731000</v>
+        <v>34996000</v>
       </c>
       <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bekobod Qog'oz MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>241436191</t>
+          <t>286584545</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000901048197001</t>
+          <t>20208000782827859001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №55/26</t>
+          <t>Предоплата за материалы по дог. №86/26</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>144256000</v>
+        <v>97670000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46266</v>
+        <v>46244</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>11937000</v>
+        <v>48552000</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>231709008</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000768612620001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4097</t>
+          <t>Предоплата за материалы по договору №164/26</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>132319000</v>
+        <v>49118000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46269</v>
+        <v>46244</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>7604000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>94479000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>231709008</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000768612620001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lv h/f №7571</t>
+          <t>Предоплата за материалы по договору №49/26</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>139923000</v>
+        <v>-45361000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46272</v>
+        <v>46245</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>51922000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>12693000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>231709008</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000768612620001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4472 07.09.2026, QQS bilan</t>
+          <t>Оплата за товары согласно с/ф №2713</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>191845000</v>
+        <v>-58054000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46272</v>
+        <v>46246</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>18884000</v>
+        <v>3054000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Durdona Yog'och AJ</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>229521083</t>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000152655598001</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №20/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №60/26, QQS 12%</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>210729000</v>
+        <v>-55000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46272</v>
+        <v>46247</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>14233000</v>
+        <v>13068000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ziyo Polimer AJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>320880818</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000860594803001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3816,752 +3826,757 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Shartnoma №141/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №114/26 от 13.08.2026</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>224962000</v>
+        <v>-41932000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46272</v>
+        <v>46247</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>10880000</v>
+        <v>5018000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Shartnoma №232/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №14/26 от 13.08.2026</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>235842000</v>
+        <v>-36914000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46272</v>
+        <v>46247</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>7538000</v>
+        <v>3025000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Urganch Qog'oz AJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>259567198</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000793787232001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Shartnoma №29/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №43/26 от 13.08.2026</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>243380000</v>
+        <v>-33889000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46272</v>
+        <v>46248</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>5416000</v>
+        <v>5458000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ilhom Meva-Sabzavot MChJ</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>380028234</t>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000449433319001</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Shartnoma №20/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №171/26, НДС 12%</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>248796000</v>
+        <v>-28431000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46272</v>
+        <v>46248</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n">
-        <v>4719000</v>
-      </c>
+      <c r="C94" s="2" t="n">
+        <v>3469000</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bekobod Agro Servis XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>225729517</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000665211036001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №296/26, НДС 12%</t>
+          <t>Уплата социального налога за июль</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>253515000</v>
+        <v>-31900000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46272</v>
+        <v>46248</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>10010000</v>
+        <v>3469000</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>310118821</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000514152594001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9148</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>243505000</v>
+        <v>-35369000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46272</v>
+        <v>46251</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>29729000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>14678000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Предоплата за товар по договору №219/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>213776000</v>
+        <v>-20691000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46273</v>
+        <v>46251</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>29136000</v>
+        <v>13795000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8200 08.09.2026, QQS bilan</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №255/26 ОТ 17.08.2026</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>242912000</v>
+        <v>-6896000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46273</v>
+        <v>46251</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>5927000</v>
+        <v>8325000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Durdona Yog' Zavodi MChJ</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>312489938</t>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000441885782001</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Shartnoma №13/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9091</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>248839000</v>
+        <v>1429000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46273</v>
+        <v>46251</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>4743000</v>
+        <v>4888000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bekobod Agro Servis XK</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>225729517</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000665211036001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №166/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №135/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>253582000</v>
+        <v>6317000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46274</v>
+        <v>46251</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>5547000</v>
+        <v>2974000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Durdona Yog' Zavodi MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>312489938</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000441885782001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №3522 ОТ 09.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №83/26, QQS 12%</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>259129000</v>
+        <v>9291000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46274</v>
+        <v>46251</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>4555000</v>
+        <v>2861000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bekobod Agro Servis XK</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>225729517</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000665211036001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2455 09.09.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7782 17.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>263684000</v>
+        <v>12152000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46274</v>
+        <v>46251</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>4258000</v>
+        <v>23867000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shahrisabz Qurilish Materiallari AJ</t>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>374593064</t>
+          <t>231709008</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000122515239001</t>
+          <t>20208000768612620001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №37/21</t>
+          <t>Оплата за упаковочные материалы, с/ф №1017</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>259426000</v>
+        <v>-11715000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46275</v>
+        <v>46251</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>145276000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>26379000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>211882155</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000415259485001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №145/26, QQS 12%</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №62/26</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>404702000</v>
+        <v>-38094000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46275</v>
+        <v>46252</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>5104000</v>
+        <v>7014000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №117/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №5054 от 18.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>409806000</v>
+        <v>-31080000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46275</v>
+        <v>46253</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>5018000</v>
+        <v>6508000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bog'ishamol Polimer MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>221511960</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000866800706001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №16/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №104/26, НДС 12%</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>414824000</v>
+        <v>-24572000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46275</v>
+        <v>46253</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>5130000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>3751000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>310118821</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000514152594001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №265/26</t>
+          <t>Предоплата за товар по договору №52/26 от 19.08.2026</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>409694000</v>
+        <v>-20821000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46275</v>
+        <v>46254</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>12794000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>2607000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bekobod Qog'oz MChJ</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>241436191</t>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000901048197001</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4510</t>
+          <t>Оплата по счет-фактуре №5214 за поставленный товар</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>396900000</v>
+        <v>-18214000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46276</v>
+        <v>46258</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>4419000</v>
+        <v>6969000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Urganch Qog'oz AJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>259567198</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000793787232001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7283</t>
+          <t>Предоплата за товар по дог. №135/26 от 24.08.2026</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>401319000</v>
+        <v>-11245000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46276</v>
+        <v>46258</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>14003000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>4102000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Bekobod Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>310118821</t>
+          <t>288081838</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000514152594001</t>
+          <t>20208000059480364001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4571,1197 +4586,1182 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №283/26</t>
+          <t>Shartnoma №37/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>387316000</v>
+        <v>-7143000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46279</v>
+        <v>46258</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>17752000</v>
+        <v>3523000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Durdona Yog' Zavodi MChJ</t>
+          <t>Jizzax Mebel MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>312489938</t>
+          <t>365971740</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000441885782001</t>
+          <t>20208000132706714001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №7539 ОТ 14.09.2026, В Т.Ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №5273 ОТ 24.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>405068000</v>
+        <v>-3620000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46279</v>
+        <v>46258</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>5421000</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>2277000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000356622702001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №190/26 от 14.09.2026</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>410489000</v>
+        <v>-5897000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46279</v>
+        <v>46258</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>8858000</v>
+        <v>6090000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №139/26</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>401631000</v>
+        <v>-11987000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46279</v>
+        <v>46258</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>26238000</v>
+        <v>25150000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Termiz Plastik MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>310118821</t>
+          <t>372951786</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000514152594001</t>
+          <t>20208000521103661001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1687</t>
+          <t>Оплата за упаковочные материалы, с/ф №5270</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>375393000</v>
+        <v>-37137000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46279</v>
+        <v>46259</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>31091000</v>
+        <v>27900000</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>203987480</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-8946)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>16307000267556002417</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №250</t>
+          <t>Kredit shartnomasi L-2025-8946 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>344302000</v>
+        <v>-65037000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46279</v>
+        <v>46260</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>60138000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>5068000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Termiz Qurilish Materiallari MChJ</t>
+          <t>Urganch Qog'oz AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>339985857</t>
+          <t>259567198</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000510257966001</t>
+          <t>20208000793787232001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №45/26</t>
+          <t>Оплата за товар по с/ф №9561 от 26.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>284164000</v>
+        <v>-59969000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46280</v>
+        <v>46261</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>4054000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>17187000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq avgust 2026</t>
+          <t>Оплата за продукцию по договору №274/26, НДС 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>280110000</v>
+        <v>-42782000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46280</v>
+        <v>46262</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>4054000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>15152000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>JShDS avgust oyi uchun</t>
+          <t>Оплата за продукцию по договору №39/26, НДС 12%</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>276056000</v>
+        <v>-27630000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46280</v>
+        <v>46262</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>9367000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>2603000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4265</t>
+          <t>Предоплата за товар по договору №89/26 от 28.08.2026</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>266689000</v>
+        <v>-25027000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46282</v>
+        <v>46265</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>36593000</v>
+        <v>197978000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2799</t>
+          <t>Предоплата за товар по договору №242/26 от 31.08.2026</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>303282000</v>
+        <v>172951000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46282</v>
+        <v>46265</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>17236000</v>
+        <v>10669000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Durdona Yog' Zavodi MChJ</t>
+          <t>Ishonch Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>312489938</t>
+          <t>390403372</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000441885782001</t>
+          <t>20208000469368665001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3328</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №218</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>320518000</v>
+        <v>183620000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46282</v>
+        <v>46265</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>3509000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>386056417</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5963 17.09.2026, QQS bilan</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>324027000</v>
+        <v>183320000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46282</v>
+        <v>46265</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>50306000</v>
+        <v>46273000</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>286584545</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000782827859001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №292/26</t>
+          <t>Предоплата за материалы по дог. №217/26</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>273721000</v>
+        <v>137047000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46283</v>
+        <v>46266</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>16478000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>8410000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Termiz Qurilish Materiallari MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>339985857</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000510257966001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №107/26</t>
+          <t>Оплата за продукцию по дог. №122/26, НД 12%</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>257243000</v>
+        <v>145457000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46283</v>
+        <v>46266</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>28659000</v>
-      </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n">
+        <v>3842000</v>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>310118821</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000514152594001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №55/26</t>
+          <t>Оплата за продукцию по договору №167/26, НДС 12%</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>228584000</v>
+        <v>149299000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46283</v>
+        <v>46266</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>165858000</v>
+        <v>10958000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>286584545</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000782827859001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №93/26, QQS bilan</t>
+          <t>Предоплата за материалы по договору №240/26</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>62726000</v>
+        <v>138341000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46286</v>
+        <v>46267</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>43947000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>22846000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Durdona Yog' Zavodi MChJ</t>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>312489938</t>
+          <t>231709008</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000441885782001</t>
+          <t>20208000768612620001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №203/26, QQS 12%</t>
+          <t>Предоплата за материалы по дог. №44/26</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>106673000</v>
+        <v>115495000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46286</v>
+        <v>46272</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>12340000</v>
+        <v>12832000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9071 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №221/26, QQS 12%</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>119013000</v>
+        <v>128327000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46286</v>
+        <v>46272</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>11394000</v>
+        <v>5185000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Bahor Trans Servis AJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>311093866</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000134330849001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №4339 от 21.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №3549 за поставленный товар</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>130407000</v>
+        <v>133512000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46286</v>
+        <v>46272</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>8191000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>23899000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bekobod Dori-Darmon XK</t>
+          <t>Durdona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>390595671</t>
+          <t>211882155</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000807937872001</t>
+          <t>20208000415259485001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №279/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №7868</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>138598000</v>
+        <v>109613000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46286</v>
+        <v>46272</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" s="2" t="n">
-        <v>3867000</v>
-      </c>
+      <c r="C130" s="2" t="n">
+        <v>29729000</v>
+      </c>
+      <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>386056417</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Shartnoma №119/26 bo'yicha oldindan to'lov</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>142465000</v>
+        <v>79884000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46286</v>
+        <v>46273</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>7173000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>9126000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Denov Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>352108361</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000265559873001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
+          <t>Оплата за продукцию по дог. №221/26, НДС 12%</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>135292000</v>
+        <v>89010000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46287</v>
+        <v>46273</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>23519000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>4258000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bekobod Dori-Darmon XK</t>
+          <t>Shahrisabz Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>390595671</t>
+          <t>259306401</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000807937872001</t>
+          <t>20208000251523904001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7099</t>
+          <t>Арендная плата за сентябрь 2026 г. по дог. №33/20</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>158811000</v>
+        <v>84752000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46287</v>
+        <v>46273</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>5122000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>16327000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Termiz Plastik MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>372951786</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000521103661001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Shartnoma №281/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №35/26 от 08.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>163933000</v>
+        <v>68425000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46288</v>
+        <v>46273</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>5377000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>30652000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>286584545</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000782827859001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №6863 23.09.2026, QQS bilan</t>
+          <t>Предоплата за материалы по дог. №241/26</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>169310000</v>
+        <v>37773000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46289</v>
+        <v>46275</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>8775000</v>
+        <v>39638000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>248993854</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000188578279001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1720</t>
+          <t>Оплата за товар по счет-фактуре №8073 от 10.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>178085000</v>
+        <v>77411000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46289</v>
+        <v>46275</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>6511000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>14183000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>310118821</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000514152594001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №15/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №9160 от 10.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>171574000</v>
+        <v>91594000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46290</v>
+        <v>46275</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>7828000</v>
+        <v>11659000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Shartnoma №56/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по с/ф №1431 от 10.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>179402000</v>
+        <v>103253000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46290</v>
+        <v>46276</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n">
-        <v>2661000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n">
+        <v>4547000</v>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Bekobod Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>288081838</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000403566227001</t>
+          <t>20208000059480364001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+          <t>Оплата за продукцию по договору №40/26, НДС 12%</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>176741000</v>
+        <v>107800000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46290</v>
+        <v>46279</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n">
-        <v>5597000</v>
-      </c>
-      <c r="D139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n">
+        <v>167456000</v>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bekobod Qog'oz MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>241436191</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000901048197001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5771,232 +5771,237 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №107/26</t>
+          <t>Оплата за продукцию по договору №45/26, НДС 12%</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>171144000</v>
+        <v>275256000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46290</v>
+        <v>46279</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>13349000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n">
+        <v>11793000</v>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2733</t>
+          <t>Оплата по счет-фактуре №7093 за поставленный товар</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>157795000</v>
+        <v>287049000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46290</v>
+        <v>46279</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>27900000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>4662000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-8946)</t>
+          <t>Durdona Moy XK</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>16307000267556002417</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-8946 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата по счет-фактуре №7186 за поставленный товар</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>129895000</v>
+        <v>291711000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46293</v>
+        <v>46279</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>6760000</v>
-      </c>
+      <c r="C142" s="2" t="n">
+        <v>4054000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №290/26, QQS 12%</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>136655000</v>
+        <v>287657000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46293</v>
+        <v>46279</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>6601000</v>
+        <v>4054000</v>
       </c>
       <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>203987480</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000251659902001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTN. №188/26, QQS BILAN</t>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>130054000</v>
+        <v>283603000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46293</v>
+        <v>46280</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>9044000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>4786000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>310118821</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000514152594001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №60/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2317 15.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>121010000</v>
+        <v>288389000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46293</v>
+        <v>46281</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>25497000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>29718000</v>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bekobod Qog'oz MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>241436191</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000901048197001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6006,111 +6011,986 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №227/26</t>
+          <t>Оплата за товар по счет-фактуре №113 от 16.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>95513000</v>
+        <v>318107000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46295</v>
+        <v>46281</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>49187000</v>
+        <v>6853000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Durdona Moy XK</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>386056417</t>
+          <t>305641799</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000929261521001</t>
+          <t>20208000926152182001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №701</t>
+          <t>Оплата за товар по счет-фактуре №5659 от 16.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>144700000</v>
+        <v>324960000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46295</v>
+        <v>46282</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
-      <c r="C147" s="2" t="n">
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>13322000</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Durdona Moy XK</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>305641799</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>20208000926152182001</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №258/26 от 17.09.2026</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>338282000</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B148" t="n">
+        <v>240</v>
+      </c>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n">
+        <v>6859000</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Durdona Moy XK</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>305641799</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>20208000926152182001</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №63/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>345141000</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B149" t="n">
+        <v>241</v>
+      </c>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>78374000</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>248993854</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>20208000188578279001</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №183/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>423515000</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B150" t="n">
+        <v>242</v>
+      </c>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>9446000</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Durdona Moy XK</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>305641799</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>20208000926152182001</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №1473 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>432961000</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B151" t="n">
+        <v>243</v>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>22849000</v>
+      </c>
+      <c r="D151" s="2" t="n"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Durdona Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>211882155</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>20208000415259485001</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Оплата за сырье по договору №219/26 от 18.09.2026, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>410112000</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B152" t="n">
+        <v>244</v>
+      </c>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n">
+        <v>31208000</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Durdona Moy XK</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>305641799</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>20208000926152182001</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №188/26 от 21.09.2026</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>441320000</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B153" t="n">
+        <v>245</v>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>11659000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>231709008</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>20208000768612620001</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно с/ф №9494</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>429661000</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B154" t="n">
+        <v>246</v>
+      </c>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>8937000</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Urganch Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>259567198</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>20208000793787232001</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4760</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>438598000</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B155" t="n">
+        <v>247</v>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>7008000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>НДС за август 2026 г.</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>431590000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B156" t="n">
+        <v>248</v>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>16853000</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Oqtosh Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>231709008</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20208000768612620001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно с/ф №1694</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>414737000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B157" t="n">
+        <v>249</v>
+      </c>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>6133000</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Kamalak Meva Eksport MChJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>251196048</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000680070639001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №1001 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>420870000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B158" t="n">
+        <v>250</v>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>76332000</v>
+      </c>
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Urganch Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>286584545</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000782827859001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №543</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>344538000</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B159" t="n">
+        <v>251</v>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>264287000</v>
+      </c>
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Urganch Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>286584545</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000782827859001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №2947</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>80251000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B160" t="n">
+        <v>252</v>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>27900000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-8946)</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>16307000267556002417</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Kredit shartnomasi L-2025-8946 bo'yicha navbatdagi to'lov (09.2026)</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>52351000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B161" t="n">
+        <v>253</v>
+      </c>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>20723000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Ishonch Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>390403372</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000469368665001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №2978 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>73074000</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B162" t="n">
+        <v>254</v>
+      </c>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n">
+        <v>19463000</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Durdona Moy XK</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>305641799</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000926152182001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №13/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>92537000</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B163" t="n">
+        <v>255</v>
+      </c>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>11064000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Durdona Moy XK</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>305641799</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000926152182001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №7977 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>103601000</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B164" t="n">
+        <v>256</v>
+      </c>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>10318000</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Sharq Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>291079198</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000100416112001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №161/26 от 28.09.2026</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>113919000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B165" t="n">
+        <v>257</v>
+      </c>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n">
+        <v>6206000</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Durdona Moy XK</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>305641799</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000926152182001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №2384 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>120125000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B166" t="n">
+        <v>258</v>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>2661000</v>
+      </c>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000356622702001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию согласно счету</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>117464000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B167" t="n">
+        <v>259</v>
+      </c>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n">
+        <v>7122000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Ishonch Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>390403372</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000469368665001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №148/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>124586000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B168" t="n">
+        <v>260</v>
+      </c>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n">
+        <v>20114000</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Kamalak Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>248993854</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000188578279001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №4912 от 30.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>144700000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B169" t="n">
+        <v>261</v>
+      </c>
+      <c r="C169" s="2" t="n">
         <v>300000</v>
       </c>
-      <c r="D147" s="2" t="n"/>
-      <c r="E147" t="inlineStr">
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" t="inlineStr">
         <is>
           <t>Yangi Asr Bank</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>45994000900000001001</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="H169" t="inlineStr">
         <is>
           <t>01089</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="n">
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Комиссия за перевод</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
         <v>144400000</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+    <row r="170">
+      <c r="A170" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C148" s="4" t="n">
-        <v>1636174000</v>
-      </c>
-      <c r="D148" s="4" t="n">
-        <v>1652174000</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="C170" s="4" t="n">
+        <v>1578805000</v>
+      </c>
+      <c r="D170" s="4" t="n">
+        <v>1594805000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C149" s="4" t="n">
+      <c r="C171" s="4" t="n">
         <v>144400000</v>
       </c>
-      <c r="D149" s="4" t="n"/>
+      <c r="D171" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
